--- a/Pruebas calificadas/COLEGIO-LA-GIRALDA-(IED)-501_Ajustado_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-LA-GIRALDA-(IED)-501_Ajustado_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1040,11 +1036,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -1052,7 +1044,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1293,11 +1285,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -1305,7 +1293,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1546,11 +1534,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -1558,7 +1542,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1795,11 +1779,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -1807,7 +1787,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2048,11 +2028,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -2060,7 +2036,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2301,11 +2277,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -2313,7 +2285,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2554,11 +2526,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -2566,7 +2534,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2807,11 +2775,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -2819,7 +2783,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3060,11 +3024,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -3072,7 +3032,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3313,11 +3273,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -3325,7 +3281,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3566,11 +3522,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -3578,7 +3530,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3819,11 +3771,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -3831,7 +3779,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4064,11 +4012,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -4076,7 +4020,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4317,11 +4261,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -4329,7 +4269,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4570,11 +4510,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -4582,7 +4518,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4819,11 +4755,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -4831,7 +4763,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5072,11 +5004,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -5084,7 +5012,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5325,11 +5253,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -5337,7 +5261,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5578,11 +5502,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -5590,7 +5510,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5831,11 +5751,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -5843,7 +5759,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6084,11 +6000,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -6096,7 +6008,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6337,11 +6249,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -6349,7 +6257,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6590,11 +6498,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -6602,7 +6506,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6839,11 +6743,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -6851,7 +6751,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7080,11 +6980,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -7092,7 +6988,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7333,11 +7229,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -7345,7 +7237,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7586,11 +7478,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -7598,7 +7486,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7839,11 +7727,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -7851,7 +7735,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8092,11 +7976,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -8104,7 +7984,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8345,11 +8225,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -8357,7 +8233,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8598,11 +8474,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -8610,7 +8482,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8823,11 +8695,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -8835,7 +8703,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9076,11 +8944,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -9088,7 +8952,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9329,11 +9193,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -9341,7 +9201,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9582,11 +9442,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -9594,7 +9450,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9835,11 +9691,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -9847,7 +9699,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10088,11 +9940,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -10100,7 +9948,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10341,11 +10189,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -10353,7 +10197,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10594,11 +10438,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -10606,7 +10446,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10847,11 +10687,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -10859,7 +10695,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11096,11 +10932,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -11108,7 +10940,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11349,11 +11181,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -11361,7 +11189,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11602,11 +11430,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -11614,7 +11438,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11855,11 +11679,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -11867,7 +11687,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12108,11 +11928,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -12120,7 +11936,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12361,11 +12177,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -12373,7 +12185,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12614,11 +12426,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -12626,7 +12434,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12867,11 +12675,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -12879,7 +12683,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -13120,11 +12924,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -13132,7 +12932,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13373,11 +13173,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -13385,7 +13181,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13626,11 +13422,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -13638,7 +13430,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13879,11 +13671,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -13891,7 +13679,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -14132,11 +13920,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -14144,7 +13928,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -14385,11 +14169,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -14397,7 +14177,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -14638,11 +14418,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -14650,7 +14426,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -14891,11 +14667,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -14903,7 +14675,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -15140,11 +14912,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -15152,7 +14920,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -15393,11 +15161,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -15405,7 +15169,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -15638,11 +15402,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -15650,7 +15410,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -15891,11 +15651,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -15903,7 +15659,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -16144,11 +15900,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -16156,7 +15908,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -16397,11 +16149,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -16409,7 +16157,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -16650,11 +16398,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -16662,7 +16406,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -16903,11 +16647,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -16915,7 +16655,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -17156,11 +16896,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -17168,7 +16904,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -17409,11 +17145,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -17421,7 +17153,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -17662,11 +17394,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="inlineStr"/>
       <c r="B69" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -17674,7 +17402,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -17915,11 +17643,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A70" s="2" t="inlineStr"/>
       <c r="B70" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -17927,7 +17651,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -18168,11 +17892,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A71" s="2" t="inlineStr"/>
       <c r="B71" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -18180,7 +17900,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -18421,11 +18141,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A72" s="2" t="inlineStr"/>
       <c r="B72" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -18433,7 +18149,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -18674,11 +18390,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -18686,7 +18398,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -18927,11 +18639,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A74" s="2" t="inlineStr"/>
       <c r="B74" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -18939,7 +18647,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -19180,11 +18888,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A75" s="2" t="inlineStr"/>
       <c r="B75" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -19192,7 +18896,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -19433,11 +19137,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A76" s="2" t="inlineStr"/>
       <c r="B76" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -19445,7 +19145,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -19682,11 +19382,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A77" s="2" t="inlineStr"/>
       <c r="B77" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -19694,7 +19390,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -19935,11 +19631,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A78" s="2" t="inlineStr"/>
       <c r="B78" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -19947,7 +19639,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -20108,11 +19800,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A79" s="2" t="inlineStr"/>
       <c r="B79" s="2" t="inlineStr">
         <is>
           <t>111001100030</t>
@@ -20120,7 +19808,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO LA GIRALDA (IED)</t>
+          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">

--- a/Pruebas calificadas/COLEGIO-LA-GIRALDA-(IED)-501_Ajustado_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-LA-GIRALDA-(IED)-501_Ajustado_CALIFICADO.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ79"/>
+  <dimension ref="A1:AZ77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -19630,344 +19630,6 @@
         <v/>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr"/>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>111001100030</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>SHARON LIZETH RAMIREZ CORREDOR</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>1016734719</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G78" s="2" t="n">
-        <v>501</v>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>MATEMÁTICAS</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="K78" s="2" t="inlineStr"/>
-      <c r="L78" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
-      <c r="N78" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="O78" s="2" t="inlineStr"/>
-      <c r="P78" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="Q78" s="2" t="inlineStr"/>
-      <c r="R78" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="S78" s="2" t="inlineStr"/>
-      <c r="T78" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="U78" s="2" t="inlineStr"/>
-      <c r="V78" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="W78" s="2" t="inlineStr"/>
-      <c r="X78" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="Y78" s="2" t="inlineStr"/>
-      <c r="Z78" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="AA78" s="2" t="inlineStr"/>
-      <c r="AB78" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="AC78" s="2" t="inlineStr"/>
-      <c r="AD78" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="AE78" s="2" t="inlineStr"/>
-      <c r="AF78" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="AG78" s="2" t="inlineStr"/>
-      <c r="AH78" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="AI78" s="2" t="inlineStr"/>
-      <c r="AJ78" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="AK78" s="2" t="inlineStr"/>
-      <c r="AL78" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="AM78" s="2" t="inlineStr"/>
-      <c r="AN78" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="AO78" s="2" t="inlineStr"/>
-      <c r="AP78" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="AQ78" s="2" t="inlineStr"/>
-      <c r="AR78" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="AS78" s="2" t="inlineStr"/>
-      <c r="AT78" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="AU78" s="2" t="inlineStr"/>
-      <c r="AV78" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="AW78" s="5">
-        <f>COUNTIF(J78:AV78,"CORRECTO")</f>
-        <v/>
-      </c>
-      <c r="AX78" s="5">
-        <f>COUNTIF(J78:AV78,"INCORRECTO")</f>
-        <v/>
-      </c>
-      <c r="AY78" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AZ78" s="6">
-        <f>AW78/AY78</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr"/>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>111001100030</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>COLEGIO LA GIRALDA (IED) - SEDE PRINCIPAL</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>SHARON LIZETH RAMIREZ CORREDOR</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>1016734719</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G79" s="2" t="n">
-        <v>501</v>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>LENGUAJE</t>
-        </is>
-      </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="K79" s="2" t="inlineStr"/>
-      <c r="L79" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
-      <c r="N79" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="O79" s="2" t="inlineStr"/>
-      <c r="P79" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="Q79" s="2" t="inlineStr"/>
-      <c r="R79" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="S79" s="2" t="inlineStr"/>
-      <c r="T79" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="U79" s="2" t="inlineStr"/>
-      <c r="V79" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="W79" s="2" t="inlineStr"/>
-      <c r="X79" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="Y79" s="2" t="inlineStr"/>
-      <c r="Z79" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="AA79" s="2" t="inlineStr"/>
-      <c r="AB79" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="AC79" s="2" t="inlineStr"/>
-      <c r="AD79" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="AE79" s="2" t="inlineStr"/>
-      <c r="AF79" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="AG79" s="2" t="inlineStr"/>
-      <c r="AH79" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="AI79" s="2" t="inlineStr"/>
-      <c r="AJ79" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="AK79" s="2" t="inlineStr"/>
-      <c r="AL79" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="AM79" s="2" t="inlineStr"/>
-      <c r="AN79" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="AO79" s="2" t="inlineStr"/>
-      <c r="AP79" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="AQ79" s="2" t="inlineStr"/>
-      <c r="AR79" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="AS79" s="2" t="inlineStr"/>
-      <c r="AT79" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="AU79" s="2" t="inlineStr"/>
-      <c r="AV79" s="3" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
-        </is>
-      </c>
-      <c r="AW79" s="5">
-        <f>COUNTIF(J79:AV79,"CORRECTO")</f>
-        <v/>
-      </c>
-      <c r="AX79" s="5">
-        <f>COUNTIF(J79:AV79,"INCORRECTO")</f>
-        <v/>
-      </c>
-      <c r="AY79" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AZ79" s="6">
-        <f>AW79/AY79</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
